--- a/vocab_list.xlsx
+++ b/vocab_list.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>vocab</t>
   </si>
   <si>
-    <t>strudle_code</t>
+    <t>strudel_code</t>
   </si>
   <si>
     <t>n_function_example</t>
@@ -28,10 +28,28 @@
     <t>bpm</t>
   </si>
   <si>
+    <t>first_90bpm_beat</t>
+  </si>
+  <si>
+    <t>pachelbel_canon</t>
+  </si>
+  <si>
+    <t>random_whitenoice_hh_16</t>
+  </si>
+  <si>
     <t>sound("&lt;jazz:2 jazz:5 jazz:1 jazz:4&gt;*16").n("&lt;2 5 1 4&gt;*8").sound("jazz")</t>
   </si>
   <si>
     <t>setcpm(120/4)</t>
+  </si>
+  <si>
+    <t>setcpm(90/4) sound("bd:2 sd:1 [bd:2 bd:2] sd").bank("RolandTR909")</t>
+  </si>
+  <si>
+    <t>note("d a b:minor f# g d g a").sound("gm_violin").room(0.5).gain(2).adsr(".2:.8:.8:.2")</t>
+  </si>
+  <si>
+    <t>$: s("white!16").decay(sine.fast(4).range(0.05,.14)).gain(.4).sometimesBy(.1, x =&gt; x.ply("2 | 4"))</t>
   </si>
 </sst>
 </file>
@@ -389,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -408,7 +426,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -419,7 +437,40 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/vocab_list.xlsx
+++ b/vocab_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>vocab</t>
   </si>
@@ -31,12 +31,15 @@
     <t>first_90bpm_beat</t>
   </si>
   <si>
-    <t>pachelbel_canon</t>
+    <t>pachelbel</t>
   </si>
   <si>
     <t>random_whitenoice_hh_16</t>
   </si>
   <si>
+    <t>sounds</t>
+  </si>
+  <si>
     <t>sound("&lt;jazz:2 jazz:5 jazz:1 jazz:4&gt;*16").n("&lt;2 5 1 4&gt;*8").sound("jazz")</t>
   </si>
   <si>
@@ -50,6 +53,9 @@
   </si>
   <si>
     <t>$: s("white!16").decay(sine.fast(4).range(0.05,.14)).gain(.4).sometimesBy(.1, x =&gt; x.ply("2 | 4"))</t>
+  </si>
+  <si>
+    <t>gm_electric_guitar_muted gm_acoustic_bass gm_voice_oohs gm_blown_bottle sawtooth square triangle</t>
   </si>
 </sst>
 </file>
@@ -407,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -426,7 +432,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -437,7 +443,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -448,7 +454,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -459,7 +465,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -470,7 +476,18 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/vocab_list.xlsx
+++ b/vocab_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>vocab</t>
   </si>
@@ -40,6 +40,18 @@
     <t>sounds</t>
   </si>
   <si>
+    <t>scales</t>
+  </si>
+  <si>
+    <t>scale_example</t>
+  </si>
+  <si>
+    <t>banger_1</t>
+  </si>
+  <si>
+    <t>drums</t>
+  </si>
+  <si>
     <t>sound("&lt;jazz:2 jazz:5 jazz:1 jazz:4&gt;*16").n("&lt;2 5 1 4&gt;*8").sound("jazz")</t>
   </si>
   <si>
@@ -56,6 +68,18 @@
   </si>
   <si>
     <t>gm_electric_guitar_muted gm_acoustic_bass gm_voice_oohs gm_blown_bottle sawtooth square triangle</t>
+  </si>
+  <si>
+    <t>C:major A2:minor D:dorian G:mixolydian A2:minor:pentatonic F:major:pentatonic</t>
+  </si>
+  <si>
+    <t>n("0 2 4 &lt;[6,8] [7,9]&gt;").scale("F:major:pentatonic").sound("piano")</t>
+  </si>
+  <si>
+    <t>$: note("&lt;[c2 c3]*4 [bb1 bb2]*4 [f2 f3]*4 [eb2 eb3]*4&gt;").sound("gm_synth_bass_1").lpf(800) $: sound("bd*4, [~ &lt;sd cp&gt;]*2, [~ hh]*4").bank("RolandTR909") $: n(`&lt; [~ 0] 2 [0 2] [~ 2] [~ 0] 1 [0 1] [~ 1] [~ 0] 3 [0 3] [~ 3] [~ 0] 2 [0 2] [~ 2] &gt;*4`).scale("C4:minor").sound("gm_synth_strings_1")</t>
+  </si>
+  <si>
+    <t>AkaiLinn RhythmAce RolandTR808 RolandTR707 ViscoSpaceDrum</t>
   </si>
 </sst>
 </file>
@@ -413,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -432,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -443,7 +467,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -454,7 +478,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -465,7 +489,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -476,7 +500,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -487,7 +511,51 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/vocab_list.xlsx
+++ b/vocab_list.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/72348917dbfafe40/Music/Strudel/Strudel-Project-1/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_573D41EAF613C8264F2C4C6CBDA2CDF149568C0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2101366-3556-4F47-A899-7C63A8F7D609}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -67,7 +73,7 @@
     <t>$: s("white!16").decay(sine.fast(4).range(0.05,.14)).gain(.4).sometimesBy(.1, x =&gt; x.ply("2 | 4"))</t>
   </si>
   <si>
-    <t>gm_electric_guitar_muted gm_acoustic_bass gm_voice_oohs gm_blown_bottle sawtooth square triangle</t>
+    <t>gm_electric_guitar_muted \ngm_acoustic_bass \ngm_voice_oohs \ngm_blown_bottle \nsawtooth \nsquare \ntriangle</t>
   </si>
   <si>
     <t>C:major A2:minor D:dorian G:mixolydian A2:minor:pentatonic F:major:pentatonic</t>
@@ -79,14 +85,14 @@
     <t>$: note("&lt;[c2 c3]*4 [bb1 bb2]*4 [f2 f3]*4 [eb2 eb3]*4&gt;").sound("gm_synth_bass_1").lpf(800) $: sound("bd*4, [~ &lt;sd cp&gt;]*2, [~ hh]*4").bank("RolandTR909") $: n(`&lt; [~ 0] 2 [0 2] [~ 2] [~ 0] 1 [0 1] [~ 1] [~ 0] 3 [0 3] [~ 3] [~ 0] 2 [0 2] [~ 2] &gt;*4`).scale("C4:minor").sound("gm_synth_strings_1")</t>
   </si>
   <si>
-    <t>AkaiLinn RhythmAce RolandTR808 RolandTR707 ViscoSpaceDrum</t>
+    <t>AkaiLinn \nRhythmAce \nRolandTR808 \nRolandTR707 \nViscoSpaceDrum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,17 +151,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -193,7 +207,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -227,6 +241,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -261,9 +276,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -436,11 +452,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -448,7 +464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -459,7 +475,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -470,7 +486,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -481,7 +497,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -492,7 +508,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -503,7 +519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -514,7 +530,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -525,7 +541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -536,7 +552,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -547,7 +563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
